--- a/extenbooks/ES2101_extenbook.xlsx
+++ b/extenbooks/ES2101_extenbook.xlsx
@@ -1215,7 +1215,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A116"/>
+  <dimension ref="A1:A146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1275,7 +1275,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>**Status**: ingested</t>
+          <t>**Status**: study_complete</t>
         </is>
       </c>
     </row>
@@ -1883,6 +1883,204 @@
       <c r="A116" t="inlineStr">
         <is>
           <t>None. v1.0 is verbatim transcription.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>## 5. Conceptual continuity vs adjacent concepts</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>The extension proxy (v1.1 shared BEA-to-Sraffa pipeline + extended</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>BLS Employment Projections crosswalk) measures `Sraffa Curvature Index</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>distribution across aggregation levels` rather than `single-matrix CI</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>point estimates` or `Theil price-value dispersion alone` because:</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>- Source agency choice: BEA Benchmark IO at the 176/119-order detail is</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  the only published US matrix that supports the 295-aggregation rollup.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  No alternative agency provides comparable industry detail.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>- Methodology continuity: v1.0 verbatim summary stats and v1.1 full CI</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  distribution both apply Bienenfeld-line vs arc-length per p(r) curve.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Adding 2012/2017 benchmark matrices reuses the same CI = 1 − SI</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  estimator, not a substitute.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>- Disambiguation: Curvature Index (CI &lt; 0.1) is NOT the price-value</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ratio of ES2001 — CI characterizes the *shape* of p(r) over r ∈ [0, R],</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  while ES2001 reports the scalar p(r_obs)/v aggregate. Both belong to</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  the same Sraffa-stochastic-effect evidence base but answer different</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  questions and have different content_type tags.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>The book's original concept (Shaikh-Coronado-Nassif-Pires 2020 §5, p. 272)</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>was: "Sraffa price curves are close to linear" — operationalized as</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>CI &lt; 0.1 across all 295 aggregations and only 6% labor-value sign</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>switches in 2002. The modern series preserves the CI estimator and</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>aggregation-level rollup methodology while permitting the BLS</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Employment Projections crosswalk URL migration (sect300.xls → current</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>EP industry data; same agency, current URL). This is NOT a proxy</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>substitution forbidden by the No-Proxy rule because (a) BEA IO is the</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>same source family, (b) BLS Employment Projections is the same agency</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>under a renamed program — concept-identical labor input data.</t>
         </is>
       </c>
     </row>
@@ -2011,14 +2209,46 @@
           <t>ES2101-avg_CI_upper_bound</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>SHAIKH_CORONADO_NASSIF_2020_S5_SUMMARY</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Shaikh-Coronado-Nassif-Pires (2020) On the empirical regularities of Sraffa prices</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>EJEEP / Edward Elgar</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.4337/ejeep.2020.0069</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>mixed (dimensionless, count, percent)</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>single benchmark years 2002 and 2007</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>fair use of summary statistics quoted in paper text</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>salvaged_chopped_table</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2026,14 +2256,46 @@
           <t>ES2101-max_bienenfeld_deviation_pct</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SHAIKH_CORONADO_NASSIF_2020_S5_SUMMARY</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Shaikh-Coronado-Nassif-Pires (2020) On the empirical regularities of Sraffa prices</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>EJEEP / Edward Elgar</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.4337/ejeep.2020.0069</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>mixed (dimensionless, count, percent)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>single benchmark years 2002 and 2007</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>fair use of summary statistics quoted in paper text</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>salvaged_chopped_table</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2041,14 +2303,46 @@
           <t>ES2101-n_prices_switching_bienenfeld</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SHAIKH_CORONADO_NASSIF_2020_S5_SUMMARY</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Shaikh-Coronado-Nassif-Pires (2020) On the empirical regularities of Sraffa prices</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>EJEEP / Edward Elgar</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.4337/ejeep.2020.0069</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>mixed (dimensionless, count, percent)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>single benchmark years 2002 and 2007</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>fair use of summary statistics quoted in paper text</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>salvaged_chopped_table</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2056,14 +2350,46 @@
           <t>ES2101-n_prices_switching_bienenfeld_pct</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>SHAIKH_CORONADO_NASSIF_2020_S5_SUMMARY</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Shaikh-Coronado-Nassif-Pires (2020) On the empirical regularities of Sraffa prices</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>EJEEP / Edward Elgar</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.4337/ejeep.2020.0069</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>mixed (dimensionless, count, percent)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>single benchmark years 2002 and 2007</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>fair use of summary statistics quoted in paper text</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>salvaged_chopped_table</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2071,14 +2397,46 @@
           <t>ES2101-n_prices_switching_value</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SHAIKH_CORONADO_NASSIF_2020_S5_SUMMARY</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Shaikh-Coronado-Nassif-Pires (2020) On the empirical regularities of Sraffa prices</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>EJEEP / Edward Elgar</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.4337/ejeep.2020.0069</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>mixed (dimensionless, count, percent)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>single benchmark years 2002 and 2007</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>fair use of summary statistics quoted in paper text</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>salvaged_chopped_table</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2086,14 +2444,46 @@
           <t>ES2101-n_prices_switching_value_pct</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>SHAIKH_CORONADO_NASSIF_2020_S5_SUMMARY</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Shaikh-Coronado-Nassif-Pires (2020) On the empirical regularities of Sraffa prices</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>EJEEP / Edward Elgar</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.4337/ejeep.2020.0069</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>mixed (dimensionless, count, percent)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>single benchmark years 2002 and 2007</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>fair use of summary statistics quoted in paper text</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>salvaged_chopped_table</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2101,14 +2491,46 @@
           <t>ES2101-n_prices_total</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>SHAIKH_CORONADO_NASSIF_2020_S5_SUMMARY</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Shaikh-Coronado-Nassif-Pires (2020) On the empirical regularities of Sraffa prices</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>EJEEP / Edward Elgar</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.4337/ejeep.2020.0069</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>mixed (dimensionless, count, percent)</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>single benchmark years 2002 and 2007</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>fair use of summary statistics quoted in paper text</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>salvaged_chopped_table</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2291,11 +2713,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2318,54 +2740,6 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>phases_completed</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>[5, 6, 7]</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>artifacts</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>{"dpr": "Technical/docs/series/ES2101_DPR.md", "epr": "Technical/docs/series/ES2101_EPR.md", "loader": "Technical/code/L01_loaders/L01_ES2101_load.py", "processor": "Technical/code/P02_processors/P02_ES2101_construct.py", "validator": "Technical/code/V03_validators/V03_ES2101_validate.py"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>last_updated</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>author</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>opus-fanout-ES</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
